--- a/artfynd/A 5527-2021 artfynd.xlsx
+++ b/artfynd/A 5527-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 5527-2021 artfynd.xlsx
+++ b/artfynd/A 5527-2021 artfynd.xlsx
@@ -1206,7 +1206,7 @@
         <v>119883674</v>
       </c>
       <c r="B6" t="n">
-        <v>57257</v>
+        <v>57267</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 5527-2021 artfynd.xlsx
+++ b/artfynd/A 5527-2021 artfynd.xlsx
@@ -1210,7 +1210,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
